--- a/database/Sample Data/excel Jan - dec today pickout.xlsx
+++ b/database/Sample Data/excel Jan - dec today pickout.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="54">
   <si>
     <t>S No</t>
   </si>
@@ -104,6 +104,9 @@
     <t>KALSHI BEASTMODE_Pkg_1</t>
   </si>
   <si>
+    <t>Sep-01</t>
+  </si>
+  <si>
     <t>TVC_BST_sh0200_conform_BG01_UGR_fRes_v001</t>
   </si>
   <si>
@@ -122,6 +125,9 @@
     <t>KALSHI BEASTMODE_Pkg_2</t>
   </si>
   <si>
+    <t>Sep-02</t>
+  </si>
+  <si>
     <t>TVC_BST_sh0390_conform_FG03_UGR_fRes_v003</t>
   </si>
   <si>
@@ -137,6 +143,9 @@
     <t>RC</t>
   </si>
   <si>
+    <t>Sep-03</t>
+  </si>
+  <si>
     <t>INV_057_0055_BG01_V001</t>
   </si>
   <si>
@@ -152,6 +161,9 @@
     <t>TRUCKS_14719_Pkg_10</t>
   </si>
   <si>
+    <t>Sep-04</t>
+  </si>
+  <si>
     <t>tmn_shots_TFO_130_bg_plate_L1_grade_v002_acescg</t>
   </si>
   <si>
@@ -165,6 +177,9 @@
   </si>
   <si>
     <t>Shiver_Pkg_4</t>
+  </si>
+  <si>
+    <t>Sep-05</t>
   </si>
   <si>
     <t>SHV_MJ_sh0620_conform_BG01_wRes_v001</t>
@@ -190,7 +205,7 @@
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="180" formatCode="mmm/yy"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -237,13 +252,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -388,7 +396,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -404,12 +412,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -769,67 +771,70 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -844,77 +849,74 @@
     <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -964,7 +966,7 @@
     <xf numFmtId="180" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -976,9 +978,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -989,9 +988,6 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1425,32 +1421,32 @@
         <v>23</v>
       </c>
       <c r="H2" s="6"/>
-      <c r="I2" s="17">
-        <v>37135</v>
+      <c r="I2" s="17" t="s">
+        <v>24</v>
       </c>
       <c r="J2" s="18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K2" s="18">
         <v>42</v>
       </c>
       <c r="L2" s="18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M2" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N2" s="20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O2" s="6"/>
       <c r="P2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q2" s="28">
+        <v>29</v>
+      </c>
+      <c r="Q2" s="26">
         <v>0.5</v>
       </c>
-      <c r="R2" s="28">
+      <c r="R2" s="26">
         <v>0.5</v>
       </c>
       <c r="S2" s="6"/>
@@ -1476,42 +1472,42 @@
         <v>120</v>
       </c>
       <c r="G3" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="11"/>
+      <c r="I3" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" s="21">
+        <v>87</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="M3" s="22"/>
+      <c r="N3" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="O3" s="22"/>
+      <c r="P3" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="21">
-        <v>37135</v>
-      </c>
-      <c r="J3" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" s="22">
-        <v>87</v>
-      </c>
-      <c r="L3" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="M3" s="23"/>
-      <c r="N3" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="O3" s="23"/>
-      <c r="P3" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q3" s="24">
+      <c r="Q3" s="23">
         <v>1</v>
       </c>
-      <c r="R3" s="23"/>
-      <c r="S3" s="23"/>
-      <c r="T3" s="23"/>
+      <c r="R3" s="22"/>
+      <c r="S3" s="22"/>
+      <c r="T3" s="22"/>
     </row>
-    <row r="4" spans="1:20">
+    <row r="4" ht="15.15" spans="1:20">
       <c r="A4" s="12">
         <v>3</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>21</v>
@@ -1520,38 +1516,38 @@
         <v>44409</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F4" s="10">
         <v>271</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H4" s="11"/>
-      <c r="I4" s="13">
-        <v>37135</v>
-      </c>
-      <c r="J4" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="K4" s="24">
+      <c r="I4" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="K4" s="23">
         <v>319</v>
       </c>
-      <c r="L4" s="24" t="s">
-        <v>31</v>
+      <c r="L4" s="23" t="s">
+        <v>33</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O4" s="11"/>
-      <c r="P4" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q4" s="24">
+      <c r="P4" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q4" s="23">
         <v>8.5</v>
       </c>
       <c r="R4" s="11"/>
@@ -1563,7 +1559,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>21</v>
@@ -1572,36 +1568,36 @@
         <v>46600</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F5" s="10">
         <v>152</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H5" s="11"/>
-      <c r="I5" s="13">
-        <v>37135</v>
+      <c r="I5" s="17" t="s">
+        <v>43</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="K5" s="25">
+        <v>44</v>
+      </c>
+      <c r="K5" s="24">
         <v>43</v>
       </c>
-      <c r="L5" s="24" t="s">
-        <v>41</v>
+      <c r="L5" s="23" t="s">
+        <v>45</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="O5" s="23"/>
+        <v>28</v>
+      </c>
+      <c r="O5" s="22"/>
       <c r="P5" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q5" s="8">
         <v>1</v>
@@ -1609,15 +1605,15 @@
       <c r="R5" s="8">
         <v>1</v>
       </c>
-      <c r="S5" s="23"/>
-      <c r="T5" s="23"/>
+      <c r="S5" s="22"/>
+      <c r="T5" s="22"/>
     </row>
-    <row r="6" spans="1:20">
+    <row r="6" ht="15.15" spans="1:20">
       <c r="A6" s="14">
         <v>5</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>21</v>
@@ -1632,42 +1628,42 @@
         <v>120</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H6" s="11"/>
-      <c r="I6" s="26">
-        <v>37135</v>
-      </c>
-      <c r="J6" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="K6" s="27">
+      <c r="I6" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="J6" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="K6" s="25">
         <v>92</v>
       </c>
-      <c r="L6" s="27" t="s">
-        <v>31</v>
+      <c r="L6" s="25" t="s">
+        <v>33</v>
       </c>
       <c r="M6" s="15" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="N6" s="15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O6" s="11"/>
       <c r="P6" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q6" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="R6" s="27" t="s">
-        <v>48</v>
+        <v>52</v>
+      </c>
+      <c r="Q6" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="R6" s="25" t="s">
+        <v>53</v>
       </c>
       <c r="S6" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="T6" s="27" t="s">
-        <v>48</v>
+        <v>53</v>
+      </c>
+      <c r="T6" s="25" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/database/Sample Data/excel Jan - dec today pickout.xlsx
+++ b/database/Sample Data/excel Jan - dec today pickout.xlsx
@@ -104,7 +104,7 @@
     <t>KALSHI BEASTMODE_Pkg_1</t>
   </si>
   <si>
-    <t>Sep-01</t>
+    <t>Sep-09</t>
   </si>
   <si>
     <t>TVC_BST_sh0200_conform_BG01_UGR_fRes_v001</t>
@@ -125,7 +125,7 @@
     <t>KALSHI BEASTMODE_Pkg_2</t>
   </si>
   <si>
-    <t>Sep-02</t>
+    <t>Sep-10</t>
   </si>
   <si>
     <t>TVC_BST_sh0390_conform_FG03_UGR_fRes_v003</t>
@@ -143,7 +143,7 @@
     <t>RC</t>
   </si>
   <si>
-    <t>Sep-03</t>
+    <t>Sep-11</t>
   </si>
   <si>
     <t>INV_057_0055_BG01_V001</t>
@@ -161,7 +161,7 @@
     <t>TRUCKS_14719_Pkg_10</t>
   </si>
   <si>
-    <t>Sep-04</t>
+    <t>Sep-12</t>
   </si>
   <si>
     <t>tmn_shots_TFO_130_bg_plate_L1_grade_v002_acescg</t>
@@ -179,7 +179,7 @@
     <t>Shiver_Pkg_4</t>
   </si>
   <si>
-    <t>Sep-05</t>
+    <t>Sep-13</t>
   </si>
   <si>
     <t>SHV_MJ_sh0620_conform_BG01_wRes_v001</t>
@@ -1502,7 +1502,7 @@
       <c r="S3" s="22"/>
       <c r="T3" s="22"/>
     </row>
-    <row r="4" ht="15.15" spans="1:20">
+    <row r="4" spans="1:20">
       <c r="A4" s="12">
         <v>3</v>
       </c>
@@ -1608,7 +1608,7 @@
       <c r="S5" s="22"/>
       <c r="T5" s="22"/>
     </row>
-    <row r="6" ht="15.15" spans="1:20">
+    <row r="6" spans="1:20">
       <c r="A6" s="14">
         <v>5</v>
       </c>

--- a/database/Sample Data/excel Jan - dec today pickout.xlsx
+++ b/database/Sample Data/excel Jan - dec today pickout.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="52">
   <si>
     <t>S No</t>
   </si>
@@ -125,9 +125,6 @@
     <t>KALSHI BEASTMODE_Pkg_2</t>
   </si>
   <si>
-    <t>Sep-10</t>
-  </si>
-  <si>
     <t>TVC_BST_sh0390_conform_FG03_UGR_fRes_v003</t>
   </si>
   <si>
@@ -159,9 +156,6 @@
   </si>
   <si>
     <t>TRUCKS_14719_Pkg_10</t>
-  </si>
-  <si>
-    <t>Sep-12</t>
   </si>
   <si>
     <t>tmn_shots_TFO_130_bg_plate_L1_grade_v002_acescg</t>
@@ -1476,16 +1470,16 @@
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="21" t="s">
         <v>31</v>
-      </c>
-      <c r="J3" s="21" t="s">
-        <v>32</v>
       </c>
       <c r="K3" s="21">
         <v>87</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M3" s="22"/>
       <c r="N3" s="8" t="s">
@@ -1502,12 +1496,12 @@
       <c r="S3" s="22"/>
       <c r="T3" s="22"/>
     </row>
-    <row r="4" spans="1:20">
+    <row r="4" ht="15.15" spans="1:20">
       <c r="A4" s="12">
         <v>3</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>21</v>
@@ -1516,29 +1510,29 @@
         <v>44409</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F4" s="10">
         <v>271</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H4" s="11"/>
       <c r="I4" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" s="23" t="s">
         <v>37</v>
-      </c>
-      <c r="J4" s="23" t="s">
-        <v>38</v>
       </c>
       <c r="K4" s="23">
         <v>319</v>
       </c>
       <c r="L4" s="23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N4" s="8" t="s">
         <v>28</v>
@@ -1559,7 +1553,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>21</v>
@@ -1568,29 +1562,29 @@
         <v>46600</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F5" s="10">
         <v>152</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H5" s="11"/>
       <c r="I5" s="17" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K5" s="24">
         <v>43</v>
       </c>
       <c r="L5" s="23" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N5" s="8" t="s">
         <v>28</v>
@@ -1608,12 +1602,12 @@
       <c r="S5" s="22"/>
       <c r="T5" s="22"/>
     </row>
-    <row r="6" spans="1:20">
+    <row r="6" ht="15.15" spans="1:20">
       <c r="A6" s="14">
         <v>5</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>21</v>
@@ -1628,42 +1622,42 @@
         <v>120</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H6" s="11"/>
       <c r="I6" s="17" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J6" s="25" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="K6" s="25">
         <v>92</v>
       </c>
       <c r="L6" s="25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M6" s="15" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="N6" s="15" t="s">
         <v>28</v>
       </c>
       <c r="O6" s="11"/>
       <c r="P6" s="15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="Q6" s="25" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R6" s="25" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="S6" s="15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="T6" s="25" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
